--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBFA8EC-F1E1-4A40-AFC8-846961AA45F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Range Down</t>
   </si>
@@ -64,11 +65,17 @@
   <si>
     <t>Range Up</t>
   </si>
+  <si>
+    <t>Zone 12</t>
+  </si>
+  <si>
+    <t>Zone 13</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -486,15 +493,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M601"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O601"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -534,8 +541,14 @@
       <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -543,7 +556,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -551,7 +564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -559,7 +572,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -567,7 +580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -575,7 +588,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -583,7 +596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -591,7 +604,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -599,7 +612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -607,7 +620,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -615,7 +628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -623,7 +636,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -631,7 +644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -639,7 +652,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -647,7 +660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>

--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBFA8EC-F1E1-4A40-AFC8-846961AA45F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02CDA0-54E1-444C-B9F7-BCA9152A9A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,9 +30,6 @@
     <t>Range Down</t>
   </si>
   <si>
-    <t>Zone 1</t>
-  </si>
-  <si>
     <t>Zone 2</t>
   </si>
   <si>
@@ -51,9 +48,6 @@
     <t>Zone 7</t>
   </si>
   <si>
-    <t>Zone 8</t>
-  </si>
-  <si>
     <t>Zone 9</t>
   </si>
   <si>
@@ -66,10 +60,16 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 12</t>
+    <t>Zone 1B</t>
   </si>
   <si>
-    <t>Zone 13</t>
+    <t>Zone 1A</t>
+  </si>
+  <si>
+    <t>Zone 8B</t>
+  </si>
+  <si>
+    <t>Zone 8A</t>
   </si>
 </sst>
 </file>
@@ -503,49 +503,49 @@
   <sheetData>
     <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">

--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02CDA0-54E1-444C-B9F7-BCA9152A9A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,12 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Range Down</t>
-  </si>
-  <si>
-    <t>Zone 1</t>
   </si>
   <si>
     <t>Zone 2</t>
@@ -50,9 +48,6 @@
     <t>Zone 7</t>
   </si>
   <si>
-    <t>Zone 8</t>
-  </si>
-  <si>
     <t>Zone 9</t>
   </si>
   <si>
@@ -64,11 +59,23 @@
   <si>
     <t>Range Up</t>
   </si>
+  <si>
+    <t>Zone 1B</t>
+  </si>
+  <si>
+    <t>Zone 1A</t>
+  </si>
+  <si>
+    <t>Zone 8B</t>
+  </si>
+  <si>
+    <t>Zone 8A</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -486,56 +493,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M601"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O601"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -543,7 +556,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -551,7 +564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -559,7 +572,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -567,7 +580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -575,7 +588,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -583,7 +596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -591,7 +604,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -599,7 +612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -607,7 +620,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -615,7 +628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -623,7 +636,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -631,7 +644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -639,7 +652,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -647,7 +660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>

--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02CDA0-54E1-444C-B9F7-BCA9152A9A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6475B88E-9105-4D5C-8FCB-2DB53723731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Range Down</t>
   </si>
@@ -60,16 +60,10 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 1B</t>
+    <t>Zone 1</t>
   </si>
   <si>
-    <t>Zone 1A</t>
-  </si>
-  <si>
-    <t>Zone 8B</t>
-  </si>
-  <si>
-    <t>Zone 8A</t>
+    <t>Zone 8</t>
   </si>
 </sst>
 </file>
@@ -494,14 +488,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O601"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M601"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="7.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -509,46 +504,40 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -556,7 +545,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -564,7 +553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -572,7 +561,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -580,7 +569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -588,7 +577,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -596,7 +585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -604,7 +593,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -612,7 +601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -620,7 +609,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -628,7 +617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -636,7 +625,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -644,7 +633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -652,7 +641,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -660,7 +649,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>
@@ -668,7 +657,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>7.51</v>
       </c>
@@ -676,7 +665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>8.01</v>
       </c>
@@ -684,7 +673,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>8.51</v>
       </c>
@@ -692,7 +681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>9.01</v>
       </c>
@@ -700,7 +689,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>9.51</v>
       </c>
@@ -708,7 +697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>10.01</v>
       </c>
@@ -716,7 +705,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>10.51</v>
       </c>
@@ -724,7 +713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>11.01</v>
       </c>
@@ -732,7 +721,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>11.51</v>
       </c>
@@ -740,7 +729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>12.01</v>
       </c>
@@ -748,7 +737,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>12.51</v>
       </c>
@@ -756,7 +745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>13.01</v>
       </c>
@@ -764,7 +753,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>13.51</v>
       </c>
@@ -772,7 +761,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>14.01</v>
       </c>
@@ -780,7 +769,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>14.51</v>
       </c>
@@ -788,7 +777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>15.01</v>
       </c>
@@ -796,7 +785,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>15.51</v>
       </c>
@@ -804,7 +793,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>16.010000000000002</v>
       </c>
@@ -812,7 +801,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>16.510000000000002</v>
       </c>
@@ -820,7 +809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>17.010000000000002</v>
       </c>
@@ -828,7 +817,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>17.510000000000002</v>
       </c>
@@ -836,7 +825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>18.010000000000002</v>
       </c>
@@ -844,7 +833,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>18.510000000000002</v>
       </c>
@@ -852,7 +841,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>19.010000000000002</v>
       </c>
@@ -860,7 +849,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>19.510000000000002</v>
       </c>
@@ -868,7 +857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>20.010000000000002</v>
       </c>
@@ -876,7 +865,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>20.51</v>
       </c>
@@ -884,7 +873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>21.01</v>
       </c>
@@ -892,7 +881,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>21.51</v>
       </c>
@@ -900,7 +889,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>22.01</v>
       </c>
@@ -908,7 +897,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>22.51</v>
       </c>
@@ -916,7 +905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>23.01</v>
       </c>
@@ -924,7 +913,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>23.51</v>
       </c>
@@ -932,7 +921,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>24.01</v>
       </c>
@@ -940,7 +929,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>24.51</v>
       </c>
@@ -948,7 +937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>25.01</v>
       </c>
@@ -956,7 +945,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>25.51</v>
       </c>
@@ -964,7 +953,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>26.01</v>
       </c>
@@ -972,7 +961,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>26.51</v>
       </c>
@@ -980,7 +969,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>27.01</v>
       </c>
@@ -988,7 +977,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>27.51</v>
       </c>
@@ -996,7 +985,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>28.01</v>
       </c>
@@ -1004,7 +993,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>28.51</v>
       </c>
@@ -1012,7 +1001,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>29.01</v>
       </c>
@@ -1020,7 +1009,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>29.51</v>
       </c>
@@ -1028,7 +1017,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>30.01</v>
       </c>
@@ -1036,7 +1025,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>30.51</v>
       </c>
@@ -1044,7 +1033,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>31.01</v>
       </c>
@@ -1052,7 +1041,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>31.51</v>
       </c>
@@ -1060,7 +1049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>32.01</v>
       </c>
@@ -1068,7 +1057,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>32.51</v>
       </c>
@@ -1076,7 +1065,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>33.01</v>
       </c>
@@ -1084,7 +1073,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>33.51</v>
       </c>
@@ -1092,7 +1081,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>34.01</v>
       </c>
@@ -1100,7 +1089,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>34.51</v>
       </c>
@@ -1108,7 +1097,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>35.01</v>
       </c>
@@ -1116,7 +1105,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>35.51</v>
       </c>
@@ -1124,7 +1113,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>36.01</v>
       </c>
@@ -1132,7 +1121,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>36.51</v>
       </c>
@@ -1140,7 +1129,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>37.01</v>
       </c>
@@ -1148,7 +1137,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>37.51</v>
       </c>
@@ -1156,7 +1145,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>38.01</v>
       </c>
@@ -1164,7 +1153,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>38.51</v>
       </c>
@@ -1172,7 +1161,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>39.01</v>
       </c>
@@ -1180,7 +1169,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>39.51</v>
       </c>
@@ -1188,7 +1177,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>40.01</v>
       </c>
@@ -1196,7 +1185,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>40.51</v>
       </c>
@@ -1204,7 +1193,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>41.01</v>
       </c>
@@ -1212,7 +1201,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>41.51</v>
       </c>
@@ -1220,7 +1209,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>42.01</v>
       </c>
@@ -1228,7 +1217,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>42.51</v>
       </c>
@@ -1236,7 +1225,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>43.01</v>
       </c>
@@ -1244,7 +1233,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>43.51</v>
       </c>
@@ -1252,7 +1241,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>44.01</v>
       </c>
@@ -1260,7 +1249,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>44.51</v>
       </c>
@@ -1268,7 +1257,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>45.01</v>
       </c>
@@ -1276,7 +1265,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>45.51</v>
       </c>
@@ -1284,7 +1273,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>46.01</v>
       </c>
@@ -1292,7 +1281,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>46.51</v>
       </c>
@@ -1300,7 +1289,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>47.01</v>
       </c>
@@ -1308,7 +1297,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>47.51</v>
       </c>
@@ -1316,7 +1305,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>48.01</v>
       </c>
@@ -1324,7 +1313,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>48.51</v>
       </c>
@@ -1332,7 +1321,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>49.01</v>
       </c>
@@ -1340,7 +1329,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>49.51</v>
       </c>
@@ -1348,7 +1337,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>50.01</v>
       </c>
@@ -1356,7 +1345,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>50.51</v>
       </c>
@@ -1364,7 +1353,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>51.01</v>
       </c>
@@ -1372,7 +1361,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>51.51</v>
       </c>
@@ -1380,7 +1369,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>52.01</v>
       </c>
@@ -1388,7 +1377,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>52.51</v>
       </c>
@@ -1396,7 +1385,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>53.01</v>
       </c>
@@ -1404,7 +1393,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>53.51</v>
       </c>
@@ -1412,7 +1401,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>54.01</v>
       </c>
@@ -1420,7 +1409,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>54.51</v>
       </c>
@@ -1428,7 +1417,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>55.01</v>
       </c>
@@ -1436,7 +1425,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>55.51</v>
       </c>
@@ -1444,7 +1433,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>56.01</v>
       </c>
@@ -1452,7 +1441,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>56.51</v>
       </c>
@@ -1460,7 +1449,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>57.01</v>
       </c>
@@ -1468,7 +1457,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>57.51</v>
       </c>
@@ -1476,7 +1465,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>58.01</v>
       </c>
@@ -1484,7 +1473,7 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>58.51</v>
       </c>
@@ -1492,7 +1481,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>59.01</v>
       </c>
@@ -1500,7 +1489,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>59.51</v>
       </c>
@@ -1508,7 +1497,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>60.01</v>
       </c>
@@ -1516,7 +1505,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>60.51</v>
       </c>
@@ -1524,7 +1513,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>61.01</v>
       </c>
@@ -1532,7 +1521,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>61.51</v>
       </c>
@@ -1540,7 +1529,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>62.01</v>
       </c>
@@ -1548,7 +1537,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>62.51</v>
       </c>
@@ -1556,7 +1545,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>63.01</v>
       </c>
@@ -1564,7 +1553,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>63.51</v>
       </c>
@@ -1572,7 +1561,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>64.010000000000005</v>
       </c>
@@ -1580,7 +1569,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>64.510000000000005</v>
       </c>
@@ -1588,7 +1577,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>65.010000000000005</v>
       </c>
@@ -1596,7 +1585,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>65.510000000000005</v>
       </c>
@@ -1604,7 +1593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>66.010000000000005</v>
       </c>
@@ -1612,7 +1601,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>66.510000000000005</v>
       </c>
@@ -1620,7 +1609,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>67.010000000000005</v>
       </c>
@@ -1628,7 +1617,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>67.510000000000005</v>
       </c>
@@ -1636,7 +1625,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>68.010000000000005</v>
       </c>
@@ -1644,7 +1633,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>68.510000000000005</v>
       </c>
@@ -1652,7 +1641,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>69.010000000000005</v>
       </c>
@@ -1660,7 +1649,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>69.510000000000005</v>
       </c>
@@ -1668,7 +1657,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>70.010000000000005</v>
       </c>
@@ -1676,7 +1665,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>70.510000000000005</v>
       </c>
@@ -1684,7 +1673,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>71.010000000000005</v>
       </c>
@@ -1692,7 +1681,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>71.510000000000005</v>
       </c>
@@ -1700,7 +1689,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>72.010000000000005</v>
       </c>
@@ -1708,7 +1697,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>72.510000000000005</v>
       </c>
@@ -1716,7 +1705,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>73.010000000000005</v>
       </c>
@@ -1724,7 +1713,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>73.510000000000005</v>
       </c>
@@ -1732,7 +1721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>74.010000000000005</v>
       </c>
@@ -1740,7 +1729,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>74.510000000000005</v>
       </c>
@@ -1748,7 +1737,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>75.010000000000005</v>
       </c>
@@ -1756,7 +1745,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>75.510000000000005</v>
       </c>
@@ -1764,7 +1753,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>76.010000000000005</v>
       </c>
@@ -1772,7 +1761,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>76.510000000000005</v>
       </c>
@@ -1780,7 +1769,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>77.010000000000005</v>
       </c>
@@ -1788,7 +1777,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>77.510000000000005</v>
       </c>
@@ -1796,7 +1785,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>78.010000000000005</v>
       </c>
@@ -1804,7 +1793,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>78.510000000000005</v>
       </c>
@@ -1812,7 +1801,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>79.010000000000005</v>
       </c>
@@ -1820,7 +1809,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>79.510000000000005</v>
       </c>
@@ -1828,7 +1817,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>80.010000000000005</v>
       </c>
@@ -1836,7 +1825,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>80.510000000000005</v>
       </c>
@@ -1844,7 +1833,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>81.010000000000005</v>
       </c>
@@ -1852,7 +1841,7 @@
         <v>81.5</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>81.510000000000005</v>
       </c>
@@ -1860,7 +1849,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>82.01</v>
       </c>
@@ -1868,7 +1857,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>82.51</v>
       </c>
@@ -1876,7 +1865,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>83.01</v>
       </c>
@@ -1884,7 +1873,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>83.51</v>
       </c>
@@ -1892,7 +1881,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>84.01</v>
       </c>
@@ -1900,7 +1889,7 @@
         <v>84.5</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>84.51</v>
       </c>
@@ -1908,7 +1897,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>85.01</v>
       </c>
@@ -1916,7 +1905,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>85.51</v>
       </c>
@@ -1924,7 +1913,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>86.01</v>
       </c>
@@ -1932,7 +1921,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>86.51</v>
       </c>
@@ -1940,7 +1929,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>87.01</v>
       </c>
@@ -1948,7 +1937,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>87.51</v>
       </c>
@@ -1956,7 +1945,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>88.01</v>
       </c>
@@ -1964,7 +1953,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>88.51</v>
       </c>
@@ -1972,7 +1961,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>89.01</v>
       </c>
@@ -1980,7 +1969,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>89.51</v>
       </c>
@@ -1988,7 +1977,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>90.01</v>
       </c>
@@ -1996,7 +1985,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>90.51</v>
       </c>
@@ -2004,7 +1993,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>91.01</v>
       </c>
@@ -2012,7 +2001,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>91.51</v>
       </c>
@@ -2020,7 +2009,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>92.01</v>
       </c>
@@ -2028,7 +2017,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>92.51</v>
       </c>
@@ -2036,7 +2025,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>93.01</v>
       </c>
@@ -2044,7 +2033,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>93.51</v>
       </c>
@@ -2052,7 +2041,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>94.01</v>
       </c>
@@ -2060,7 +2049,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>94.51</v>
       </c>
@@ -2068,7 +2057,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>95.01</v>
       </c>
@@ -2076,7 +2065,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>95.51</v>
       </c>
@@ -2084,7 +2073,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>96.01</v>
       </c>
@@ -2092,7 +2081,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>96.51</v>
       </c>
@@ -2100,7 +2089,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>97.01</v>
       </c>
@@ -2108,7 +2097,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>97.51</v>
       </c>
@@ -2116,7 +2105,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>98.01</v>
       </c>
@@ -2124,7 +2113,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>98.51</v>
       </c>
@@ -2132,7 +2121,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>99.01</v>
       </c>
@@ -2140,7 +2129,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>99.51</v>
       </c>
@@ -2148,7 +2137,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>100.01</v>
       </c>
@@ -2156,7 +2145,7 @@
         <v>100.5</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>100.51</v>
       </c>
@@ -2164,7 +2153,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>101.01</v>
       </c>
@@ -2172,7 +2161,7 @@
         <v>101.5</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>101.51</v>
       </c>
@@ -2180,7 +2169,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>102.01</v>
       </c>
@@ -2188,7 +2177,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>102.51</v>
       </c>
@@ -2196,7 +2185,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>103.01</v>
       </c>
@@ -2204,7 +2193,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>103.51</v>
       </c>
@@ -2212,7 +2201,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>104.01</v>
       </c>
@@ -2220,7 +2209,7 @@
         <v>104.5</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>104.51</v>
       </c>
@@ -2228,7 +2217,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>105.01</v>
       </c>
@@ -2236,7 +2225,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>105.51</v>
       </c>
@@ -2244,7 +2233,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>106.01</v>
       </c>
@@ -2252,7 +2241,7 @@
         <v>106.5</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>106.51</v>
       </c>
@@ -2260,7 +2249,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>107.01</v>
       </c>
@@ -2268,7 +2257,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>107.51</v>
       </c>
@@ -2276,7 +2265,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>108.01</v>
       </c>
@@ -2284,7 +2273,7 @@
         <v>108.5</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>108.51</v>
       </c>
@@ -2292,7 +2281,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>109.01</v>
       </c>
@@ -2300,7 +2289,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>109.51</v>
       </c>
@@ -2308,7 +2297,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>110.01</v>
       </c>
@@ -2316,7 +2305,7 @@
         <v>110.5</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>110.51</v>
       </c>
@@ -2324,7 +2313,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>111.01</v>
       </c>
@@ -2332,7 +2321,7 @@
         <v>111.5</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>111.51</v>
       </c>
@@ -2340,7 +2329,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>112.01</v>
       </c>
@@ -2348,7 +2337,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>112.51</v>
       </c>
@@ -2356,7 +2345,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>113.01</v>
       </c>
@@ -2364,7 +2353,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>113.51</v>
       </c>
@@ -2372,7 +2361,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>114.01</v>
       </c>
@@ -2380,7 +2369,7 @@
         <v>114.5</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>114.51</v>
       </c>
@@ -2388,7 +2377,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>115.01</v>
       </c>
@@ -2396,7 +2385,7 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>115.51</v>
       </c>
@@ -2404,7 +2393,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>116.01</v>
       </c>
@@ -2412,7 +2401,7 @@
         <v>116.5</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>116.51</v>
       </c>
@@ -2420,7 +2409,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>117.01</v>
       </c>
@@ -2428,7 +2417,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>117.51</v>
       </c>
@@ -2436,7 +2425,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>118.01</v>
       </c>
@@ -2444,7 +2433,7 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>118.51</v>
       </c>
@@ -2452,7 +2441,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>119.01</v>
       </c>
@@ -2460,7 +2449,7 @@
         <v>119.5</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>119.51</v>
       </c>
@@ -2468,7 +2457,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>120.01</v>
       </c>
@@ -2476,7 +2465,7 @@
         <v>120.5</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>120.51</v>
       </c>
@@ -2484,7 +2473,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>121.01</v>
       </c>
@@ -2492,7 +2481,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>121.51</v>
       </c>
@@ -2500,7 +2489,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>122.01</v>
       </c>
@@ -2508,7 +2497,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>122.51</v>
       </c>
@@ -2516,7 +2505,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>123.01</v>
       </c>
@@ -2524,7 +2513,7 @@
         <v>123.5</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>123.51</v>
       </c>
@@ -2532,7 +2521,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>124.01</v>
       </c>
@@ -2540,7 +2529,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>124.51</v>
       </c>
@@ -2548,7 +2537,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>125.01</v>
       </c>
@@ -2556,7 +2545,7 @@
         <v>125.5</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>125.51</v>
       </c>
@@ -2564,7 +2553,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>126.01</v>
       </c>
@@ -2572,7 +2561,7 @@
         <v>126.5</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>126.51</v>
       </c>
@@ -2580,7 +2569,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>127.01</v>
       </c>
@@ -2588,7 +2577,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>127.51</v>
       </c>
@@ -2596,7 +2585,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>128.01</v>
       </c>
@@ -2604,7 +2593,7 @@
         <v>128.5</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>128.51</v>
       </c>
@@ -2612,7 +2601,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>129.01</v>
       </c>
@@ -2620,7 +2609,7 @@
         <v>129.5</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>129.51</v>
       </c>
@@ -2628,7 +2617,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>130.01</v>
       </c>
@@ -2636,7 +2625,7 @@
         <v>130.5</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>130.51</v>
       </c>
@@ -2644,7 +2633,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>131.01</v>
       </c>
@@ -2652,7 +2641,7 @@
         <v>131.5</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>131.51</v>
       </c>
@@ -2660,7 +2649,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>132.01</v>
       </c>
@@ -2668,7 +2657,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>132.51</v>
       </c>
@@ -2676,7 +2665,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>133.01</v>
       </c>
@@ -2684,7 +2673,7 @@
         <v>133.5</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>133.51</v>
       </c>
@@ -2692,7 +2681,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>134.01</v>
       </c>
@@ -2700,7 +2689,7 @@
         <v>134.5</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>134.51</v>
       </c>
@@ -2708,7 +2697,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>135.01</v>
       </c>
@@ -2716,7 +2705,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>135.51</v>
       </c>
@@ -2724,7 +2713,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>136.01</v>
       </c>
@@ -2732,7 +2721,7 @@
         <v>136.5</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>136.51</v>
       </c>
@@ -2740,7 +2729,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>137.01</v>
       </c>
@@ -2748,7 +2737,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>137.51</v>
       </c>
@@ -2756,7 +2745,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>138.01</v>
       </c>
@@ -2764,7 +2753,7 @@
         <v>138.5</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>138.51</v>
       </c>
@@ -2772,7 +2761,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>139.01</v>
       </c>
@@ -2780,7 +2769,7 @@
         <v>139.5</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>139.51</v>
       </c>
@@ -2788,7 +2777,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>140.01</v>
       </c>
@@ -2796,7 +2785,7 @@
         <v>140.5</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>140.51</v>
       </c>
@@ -2804,7 +2793,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>141.01</v>
       </c>
@@ -2812,7 +2801,7 @@
         <v>141.5</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>141.51</v>
       </c>
@@ -2820,7 +2809,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>142.01</v>
       </c>
@@ -2828,7 +2817,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>142.51</v>
       </c>
@@ -2836,7 +2825,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>143.01</v>
       </c>
@@ -2844,7 +2833,7 @@
         <v>143.5</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>143.51</v>
       </c>
@@ -2852,7 +2841,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>144.01</v>
       </c>
@@ -2860,7 +2849,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>144.51</v>
       </c>
@@ -2868,7 +2857,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>145.01</v>
       </c>
@@ -2876,7 +2865,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>145.51</v>
       </c>
@@ -2884,7 +2873,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>146.01</v>
       </c>
@@ -2892,7 +2881,7 @@
         <v>146.5</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>146.51</v>
       </c>
@@ -2900,7 +2889,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>147.01</v>
       </c>
@@ -2908,7 +2897,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>147.51</v>
       </c>
@@ -2916,7 +2905,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>148.01</v>
       </c>
@@ -2924,7 +2913,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>148.51</v>
       </c>
@@ -2932,7 +2921,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>149.01</v>
       </c>
@@ -2940,7 +2929,7 @@
         <v>149.5</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>149.51</v>
       </c>
@@ -2948,7 +2937,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>150.01</v>
       </c>
@@ -2956,7 +2945,7 @@
         <v>150.5</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>150.51</v>
       </c>
@@ -2964,7 +2953,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>151.01</v>
       </c>
@@ -2972,7 +2961,7 @@
         <v>151.5</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>151.51</v>
       </c>
@@ -2980,7 +2969,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>152.01</v>
       </c>
@@ -2988,7 +2977,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>152.51</v>
       </c>
@@ -2996,7 +2985,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>153.01</v>
       </c>
@@ -3004,7 +2993,7 @@
         <v>153.5</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>153.51</v>
       </c>
@@ -3012,7 +3001,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>154.01</v>
       </c>
@@ -3020,7 +3009,7 @@
         <v>154.5</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>154.51</v>
       </c>
@@ -3028,7 +3017,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>155.01</v>
       </c>
@@ -3036,7 +3025,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>155.51</v>
       </c>
@@ -3044,7 +3033,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>156.01</v>
       </c>
@@ -3052,7 +3041,7 @@
         <v>156.5</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>156.51</v>
       </c>
@@ -3060,7 +3049,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>157.01</v>
       </c>
@@ -3068,7 +3057,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>157.51</v>
       </c>
@@ -3076,7 +3065,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>158.01</v>
       </c>
@@ -3084,7 +3073,7 @@
         <v>158.5</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>158.51</v>
       </c>
@@ -3092,7 +3081,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>159.01</v>
       </c>
@@ -3100,7 +3089,7 @@
         <v>159.5</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>159.51</v>
       </c>
@@ -3108,7 +3097,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>160.01</v>
       </c>
@@ -3116,7 +3105,7 @@
         <v>160.5</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>160.51</v>
       </c>
@@ -3124,7 +3113,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>161.01</v>
       </c>
@@ -3132,7 +3121,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>161.51</v>
       </c>
@@ -3140,7 +3129,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>162.01</v>
       </c>
@@ -3148,7 +3137,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>162.51</v>
       </c>
@@ -3156,7 +3145,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>163.01</v>
       </c>
@@ -3164,7 +3153,7 @@
         <v>163.5</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>163.51</v>
       </c>
@@ -3172,7 +3161,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>164.01</v>
       </c>
@@ -3180,7 +3169,7 @@
         <v>164.5</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>164.51</v>
       </c>
@@ -3188,7 +3177,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>165.01</v>
       </c>
@@ -3196,7 +3185,7 @@
         <v>165.5</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>165.51</v>
       </c>
@@ -3204,7 +3193,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>166.01</v>
       </c>
@@ -3212,7 +3201,7 @@
         <v>166.5</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>166.51</v>
       </c>
@@ -3220,7 +3209,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>167.01</v>
       </c>
@@ -3228,7 +3217,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>167.51</v>
       </c>
@@ -3236,7 +3225,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>168.01</v>
       </c>
@@ -3244,7 +3233,7 @@
         <v>168.5</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>168.51</v>
       </c>
@@ -3252,7 +3241,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>169.01</v>
       </c>
@@ -3260,7 +3249,7 @@
         <v>169.5</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>169.51</v>
       </c>
@@ -3268,7 +3257,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>170.01</v>
       </c>
@@ -3276,7 +3265,7 @@
         <v>170.5</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>170.51</v>
       </c>
@@ -3284,7 +3273,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>171.01</v>
       </c>
@@ -3292,7 +3281,7 @@
         <v>171.5</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>171.51</v>
       </c>
@@ -3300,7 +3289,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>172.01</v>
       </c>
@@ -3308,7 +3297,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>172.51</v>
       </c>
@@ -3316,7 +3305,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>173.01</v>
       </c>
@@ -3324,7 +3313,7 @@
         <v>173.5</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>173.51</v>
       </c>
@@ -3332,7 +3321,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>174.01</v>
       </c>
@@ -3340,7 +3329,7 @@
         <v>174.5</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>174.51</v>
       </c>
@@ -3348,7 +3337,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>175.01</v>
       </c>
@@ -3356,7 +3345,7 @@
         <v>175.5</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>175.51</v>
       </c>
@@ -3364,7 +3353,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>176.01</v>
       </c>
@@ -3372,7 +3361,7 @@
         <v>176.5</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>176.51</v>
       </c>
@@ -3380,7 +3369,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>177.01</v>
       </c>
@@ -3388,7 +3377,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>177.51</v>
       </c>
@@ -3396,7 +3385,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>178.01</v>
       </c>
@@ -3404,7 +3393,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>178.51</v>
       </c>
@@ -3412,7 +3401,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>179.01</v>
       </c>
@@ -3420,7 +3409,7 @@
         <v>179.5</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>179.51</v>
       </c>
@@ -3428,7 +3417,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>180.01</v>
       </c>
@@ -3436,7 +3425,7 @@
         <v>180.5</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>180.51</v>
       </c>
@@ -3444,7 +3433,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>181.01</v>
       </c>
@@ -3452,7 +3441,7 @@
         <v>181.5</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>181.51</v>
       </c>
@@ -3460,7 +3449,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>182.01</v>
       </c>
@@ -3468,7 +3457,7 @@
         <v>182.5</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>182.51</v>
       </c>
@@ -3476,7 +3465,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>183.01</v>
       </c>
@@ -3484,7 +3473,7 @@
         <v>183.5</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>183.51</v>
       </c>
@@ -3492,7 +3481,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>184.01</v>
       </c>
@@ -3500,7 +3489,7 @@
         <v>184.5</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>184.51</v>
       </c>
@@ -3508,7 +3497,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>185.01</v>
       </c>
@@ -3516,7 +3505,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>185.51</v>
       </c>
@@ -3524,7 +3513,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>186.01</v>
       </c>
@@ -3532,7 +3521,7 @@
         <v>186.5</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>186.51</v>
       </c>
@@ -3540,7 +3529,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>187.01</v>
       </c>
@@ -3548,7 +3537,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>187.51</v>
       </c>
@@ -3556,7 +3545,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>188.01</v>
       </c>
@@ -3564,7 +3553,7 @@
         <v>188.5</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>188.51</v>
       </c>
@@ -3572,7 +3561,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>189.01</v>
       </c>
@@ -3580,7 +3569,7 @@
         <v>189.5</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>189.51</v>
       </c>
@@ -3588,7 +3577,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>190.01</v>
       </c>
@@ -3596,7 +3585,7 @@
         <v>190.5</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>190.51</v>
       </c>
@@ -3604,7 +3593,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>191.01</v>
       </c>
@@ -3612,7 +3601,7 @@
         <v>191.5</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>191.51</v>
       </c>
@@ -3620,7 +3609,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>192.01</v>
       </c>
@@ -3628,7 +3617,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>192.51</v>
       </c>
@@ -3636,7 +3625,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>193.01</v>
       </c>
@@ -3644,7 +3633,7 @@
         <v>193.5</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>193.51</v>
       </c>
@@ -3652,7 +3641,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>194.01</v>
       </c>
@@ -3660,7 +3649,7 @@
         <v>194.5</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>194.51</v>
       </c>
@@ -3668,7 +3657,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>195.01</v>
       </c>
@@ -3676,7 +3665,7 @@
         <v>195.5</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>195.51</v>
       </c>
@@ -3684,7 +3673,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>196.01</v>
       </c>
@@ -3692,7 +3681,7 @@
         <v>196.5</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>196.51</v>
       </c>
@@ -3700,7 +3689,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>197.01</v>
       </c>
@@ -3708,7 +3697,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>197.51</v>
       </c>
@@ -3716,7 +3705,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>198.01</v>
       </c>
@@ -3724,7 +3713,7 @@
         <v>198.5</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>198.51</v>
       </c>
@@ -3732,7 +3721,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>199.01</v>
       </c>
@@ -3740,7 +3729,7 @@
         <v>199.5</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>199.51</v>
       </c>
@@ -3748,7 +3737,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>200.01</v>
       </c>
@@ -3756,7 +3745,7 @@
         <v>200.5</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>200.51</v>
       </c>
@@ -3764,7 +3753,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>201.01</v>
       </c>
@@ -3772,7 +3761,7 @@
         <v>201.5</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>201.51</v>
       </c>
@@ -3780,7 +3769,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>202.01</v>
       </c>
@@ -3788,7 +3777,7 @@
         <v>202.5</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>202.51</v>
       </c>
@@ -3796,7 +3785,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>203.01</v>
       </c>
@@ -3804,7 +3793,7 @@
         <v>203.5</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>203.51</v>
       </c>
@@ -3812,7 +3801,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>204.01</v>
       </c>
@@ -3820,7 +3809,7 @@
         <v>204.5</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>204.51</v>
       </c>
@@ -3828,7 +3817,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>205.01</v>
       </c>
@@ -3836,7 +3825,7 @@
         <v>205.5</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>205.51</v>
       </c>
@@ -3844,7 +3833,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>206.01</v>
       </c>
@@ -3852,7 +3841,7 @@
         <v>206.5</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>206.51</v>
       </c>
@@ -3860,7 +3849,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>207.01</v>
       </c>
@@ -3868,7 +3857,7 @@
         <v>207.5</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>207.51</v>
       </c>
@@ -3876,7 +3865,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>208.01</v>
       </c>
@@ -3884,7 +3873,7 @@
         <v>208.5</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>208.51</v>
       </c>
@@ -3892,7 +3881,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>209.01</v>
       </c>
@@ -3900,7 +3889,7 @@
         <v>209.5</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>209.51</v>
       </c>
@@ -3908,7 +3897,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>210.01</v>
       </c>
@@ -3916,7 +3905,7 @@
         <v>210.5</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>210.51</v>
       </c>
@@ -3924,7 +3913,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>211.01</v>
       </c>
@@ -3932,7 +3921,7 @@
         <v>211.5</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>211.51</v>
       </c>
@@ -3940,7 +3929,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>212.01</v>
       </c>
@@ -3948,7 +3937,7 @@
         <v>212.5</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>212.51</v>
       </c>
@@ -3956,7 +3945,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>213.01</v>
       </c>
@@ -3964,7 +3953,7 @@
         <v>213.5</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>213.51</v>
       </c>
@@ -3972,7 +3961,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>214.01</v>
       </c>
@@ -3980,7 +3969,7 @@
         <v>214.5</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>214.51</v>
       </c>
@@ -3988,7 +3977,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>215.01</v>
       </c>
@@ -3996,7 +3985,7 @@
         <v>215.5</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>215.51</v>
       </c>
@@ -4004,7 +3993,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>216.01</v>
       </c>
@@ -4012,7 +4001,7 @@
         <v>216.5</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>216.51</v>
       </c>
@@ -4020,7 +4009,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>217.01</v>
       </c>
@@ -4028,7 +4017,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>217.51</v>
       </c>
@@ -4036,7 +4025,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>218.01</v>
       </c>
@@ -4044,7 +4033,7 @@
         <v>218.5</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>218.51</v>
       </c>
@@ -4052,7 +4041,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>219.01</v>
       </c>
@@ -4060,7 +4049,7 @@
         <v>219.5</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>219.51</v>
       </c>
@@ -4068,7 +4057,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>220.01</v>
       </c>
@@ -4076,7 +4065,7 @@
         <v>220.5</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>220.51</v>
       </c>
@@ -4084,7 +4073,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>221.01</v>
       </c>
@@ -4092,7 +4081,7 @@
         <v>221.5</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>221.51</v>
       </c>
@@ -4100,7 +4089,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>222.01</v>
       </c>
@@ -4108,7 +4097,7 @@
         <v>222.5</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>222.51</v>
       </c>
@@ -4116,7 +4105,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>223.01</v>
       </c>
@@ -4124,7 +4113,7 @@
         <v>223.5</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>223.51</v>
       </c>
@@ -4132,7 +4121,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>224.01</v>
       </c>
@@ -4140,7 +4129,7 @@
         <v>224.5</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>224.51</v>
       </c>
@@ -4148,7 +4137,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>225.01</v>
       </c>
@@ -4156,7 +4145,7 @@
         <v>225.5</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>225.51</v>
       </c>
@@ -4164,7 +4153,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>226.01</v>
       </c>
@@ -4172,7 +4161,7 @@
         <v>226.5</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>226.51</v>
       </c>
@@ -4180,7 +4169,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>227.01</v>
       </c>
@@ -4188,7 +4177,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>227.51</v>
       </c>
@@ -4196,7 +4185,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>228.01</v>
       </c>
@@ -4204,7 +4193,7 @@
         <v>228.5</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>228.51</v>
       </c>
@@ -4212,7 +4201,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>229.01</v>
       </c>
@@ -4220,7 +4209,7 @@
         <v>229.5</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>229.51</v>
       </c>
@@ -4228,7 +4217,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>230.01</v>
       </c>
@@ -4236,7 +4225,7 @@
         <v>230.5</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>230.51</v>
       </c>
@@ -4244,7 +4233,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>231.01</v>
       </c>
@@ -4252,7 +4241,7 @@
         <v>231.5</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>231.51</v>
       </c>
@@ -4260,7 +4249,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>232.01</v>
       </c>
@@ -4268,7 +4257,7 @@
         <v>232.5</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>232.51</v>
       </c>
@@ -4276,7 +4265,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>233.01</v>
       </c>
@@ -4284,7 +4273,7 @@
         <v>233.5</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>233.51</v>
       </c>
@@ -4292,7 +4281,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>234.01</v>
       </c>
@@ -4300,7 +4289,7 @@
         <v>234.5</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>234.51</v>
       </c>
@@ -4308,7 +4297,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>235.01</v>
       </c>
@@ -4316,7 +4305,7 @@
         <v>235.5</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>235.51</v>
       </c>
@@ -4324,7 +4313,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>236.01</v>
       </c>
@@ -4332,7 +4321,7 @@
         <v>236.5</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>236.51</v>
       </c>
@@ -4340,7 +4329,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>237.01</v>
       </c>
@@ -4348,7 +4337,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>237.51</v>
       </c>
@@ -4356,7 +4345,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>238.01</v>
       </c>
@@ -4364,7 +4353,7 @@
         <v>238.5</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>238.51</v>
       </c>
@@ -4372,7 +4361,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>239.01</v>
       </c>
@@ -4380,7 +4369,7 @@
         <v>239.5</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>239.51</v>
       </c>
@@ -4388,7 +4377,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>240.01</v>
       </c>
@@ -4396,7 +4385,7 @@
         <v>240.5</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>240.51</v>
       </c>
@@ -4404,7 +4393,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>241.01</v>
       </c>
@@ -4412,7 +4401,7 @@
         <v>241.5</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>241.51</v>
       </c>
@@ -4420,7 +4409,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>242.01</v>
       </c>
@@ -4428,7 +4417,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>242.51</v>
       </c>
@@ -4436,7 +4425,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>243.01</v>
       </c>
@@ -4444,7 +4433,7 @@
         <v>243.5</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>243.51</v>
       </c>
@@ -4452,7 +4441,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>244.01</v>
       </c>
@@ -4460,7 +4449,7 @@
         <v>244.5</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>244.51</v>
       </c>
@@ -4468,7 +4457,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>245.01</v>
       </c>
@@ -4476,7 +4465,7 @@
         <v>245.5</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>245.51</v>
       </c>
@@ -4484,7 +4473,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>246.01</v>
       </c>
@@ -4492,7 +4481,7 @@
         <v>246.5</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>246.51</v>
       </c>
@@ -4500,7 +4489,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>247.01</v>
       </c>
@@ -4508,7 +4497,7 @@
         <v>247.5</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>247.51</v>
       </c>
@@ -4516,7 +4505,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>248.01</v>
       </c>
@@ -4524,7 +4513,7 @@
         <v>248.5</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>248.51</v>
       </c>
@@ -4532,7 +4521,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>249.01</v>
       </c>
@@ -4540,7 +4529,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>249.51</v>
       </c>
@@ -4548,7 +4537,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>250.01</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>250.5</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>250.51</v>
       </c>
@@ -4564,7 +4553,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>251.01</v>
       </c>
@@ -4572,7 +4561,7 @@
         <v>251.5</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>251.51</v>
       </c>
@@ -4580,7 +4569,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>252.01</v>
       </c>
@@ -4588,7 +4577,7 @@
         <v>252.5</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>252.51</v>
       </c>
@@ -4596,7 +4585,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>253.01</v>
       </c>
@@ -4604,7 +4593,7 @@
         <v>253.5</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>253.51</v>
       </c>
@@ -4612,7 +4601,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>254.01</v>
       </c>
@@ -4620,7 +4609,7 @@
         <v>254.5</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>254.51</v>
       </c>
@@ -4628,7 +4617,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>255.01</v>
       </c>
@@ -4636,7 +4625,7 @@
         <v>255.5</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>255.51</v>
       </c>
@@ -4644,7 +4633,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>256.01</v>
       </c>
@@ -4652,7 +4641,7 @@
         <v>256.5</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>256.51</v>
       </c>
@@ -4660,7 +4649,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>257.01</v>
       </c>
@@ -4668,7 +4657,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>257.51</v>
       </c>
@@ -4676,7 +4665,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>258.01</v>
       </c>
@@ -4684,7 +4673,7 @@
         <v>258.5</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>258.51</v>
       </c>
@@ -4692,7 +4681,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>259.01</v>
       </c>
@@ -4700,7 +4689,7 @@
         <v>259.5</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>259.51</v>
       </c>
@@ -4708,7 +4697,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>260.01</v>
       </c>
@@ -4716,7 +4705,7 @@
         <v>260.5</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>260.51</v>
       </c>
@@ -4724,7 +4713,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>261.01</v>
       </c>
@@ -4732,7 +4721,7 @@
         <v>261.5</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>261.51</v>
       </c>
@@ -4740,7 +4729,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>262.01</v>
       </c>
@@ -4748,7 +4737,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>262.51</v>
       </c>
@@ -4756,7 +4745,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>263.01</v>
       </c>
@@ -4764,7 +4753,7 @@
         <v>263.5</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>263.51</v>
       </c>
@@ -4772,7 +4761,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>264.01</v>
       </c>
@@ -4780,7 +4769,7 @@
         <v>264.5</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>264.51</v>
       </c>
@@ -4788,7 +4777,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>265.01</v>
       </c>
@@ -4796,7 +4785,7 @@
         <v>265.5</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>265.51</v>
       </c>
@@ -4804,7 +4793,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>266.01</v>
       </c>
@@ -4812,7 +4801,7 @@
         <v>266.5</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>266.51</v>
       </c>
@@ -4820,7 +4809,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>267.01</v>
       </c>
@@ -4828,7 +4817,7 @@
         <v>267.5</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>267.51</v>
       </c>
@@ -4836,7 +4825,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>268.01</v>
       </c>
@@ -4844,7 +4833,7 @@
         <v>268.5</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>268.51</v>
       </c>
@@ -4852,7 +4841,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>269.01</v>
       </c>
@@ -4860,7 +4849,7 @@
         <v>269.5</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>269.51</v>
       </c>
@@ -4868,7 +4857,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>270.01</v>
       </c>
@@ -4876,7 +4865,7 @@
         <v>270.5</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>270.51</v>
       </c>
@@ -4884,7 +4873,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>271.01</v>
       </c>
@@ -4892,7 +4881,7 @@
         <v>271.5</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>271.51</v>
       </c>
@@ -4900,7 +4889,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>272.01</v>
       </c>
@@ -4908,7 +4897,7 @@
         <v>272.5</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>272.51</v>
       </c>
@@ -4916,7 +4905,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>273.01</v>
       </c>
@@ -4924,7 +4913,7 @@
         <v>273.5</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>273.51</v>
       </c>
@@ -4932,7 +4921,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>274.01</v>
       </c>
@@ -4940,7 +4929,7 @@
         <v>274.5</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>274.51</v>
       </c>
@@ -4948,7 +4937,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>275.01</v>
       </c>
@@ -4956,7 +4945,7 @@
         <v>275.5</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>275.51</v>
       </c>
@@ -4964,7 +4953,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>276.01</v>
       </c>
@@ -4972,7 +4961,7 @@
         <v>276.5</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>276.51</v>
       </c>
@@ -4980,7 +4969,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>277.01</v>
       </c>
@@ -4988,7 +4977,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>277.51</v>
       </c>
@@ -4996,7 +4985,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>278.01</v>
       </c>
@@ -5004,7 +4993,7 @@
         <v>278.5</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>278.51</v>
       </c>
@@ -5012,7 +5001,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>279.01</v>
       </c>
@@ -5020,7 +5009,7 @@
         <v>279.5</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>279.51</v>
       </c>
@@ -5028,7 +5017,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>280.01</v>
       </c>
@@ -5036,7 +5025,7 @@
         <v>280.5</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>280.51</v>
       </c>
@@ -5044,7 +5033,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>281.01</v>
       </c>
@@ -5052,7 +5041,7 @@
         <v>281.5</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>281.51</v>
       </c>
@@ -5060,7 +5049,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>282.01</v>
       </c>
@@ -5068,7 +5057,7 @@
         <v>282.5</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>282.51</v>
       </c>
@@ -5076,7 +5065,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>283.01</v>
       </c>
@@ -5084,7 +5073,7 @@
         <v>283.5</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>283.51</v>
       </c>
@@ -5092,7 +5081,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>284.01</v>
       </c>
@@ -5100,7 +5089,7 @@
         <v>284.5</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>284.51</v>
       </c>
@@ -5108,7 +5097,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>285.01</v>
       </c>
@@ -5116,7 +5105,7 @@
         <v>285.5</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>285.51</v>
       </c>
@@ -5124,7 +5113,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>286.01</v>
       </c>
@@ -5132,7 +5121,7 @@
         <v>286.5</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>286.51</v>
       </c>
@@ -5140,7 +5129,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>287.01</v>
       </c>
@@ -5148,7 +5137,7 @@
         <v>287.5</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>287.51</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>288.01</v>
       </c>
@@ -5164,7 +5153,7 @@
         <v>288.5</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>288.51</v>
       </c>
@@ -5172,7 +5161,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>289.01</v>
       </c>
@@ -5180,7 +5169,7 @@
         <v>289.5</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>289.51</v>
       </c>
@@ -5188,7 +5177,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>290.01</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>290.5</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>290.51</v>
       </c>
@@ -5204,7 +5193,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>291.01</v>
       </c>
@@ -5212,7 +5201,7 @@
         <v>291.5</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>291.51</v>
       </c>
@@ -5220,7 +5209,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>292.01</v>
       </c>
@@ -5228,7 +5217,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>292.51</v>
       </c>
@@ -5236,7 +5225,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>293.01</v>
       </c>
@@ -5244,7 +5233,7 @@
         <v>293.5</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>293.51</v>
       </c>
@@ -5252,7 +5241,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>294.01</v>
       </c>
@@ -5260,7 +5249,7 @@
         <v>294.5</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>294.51</v>
       </c>
@@ -5268,7 +5257,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>295.01</v>
       </c>
@@ -5276,7 +5265,7 @@
         <v>295.5</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>295.51</v>
       </c>
@@ -5284,7 +5273,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>296.01</v>
       </c>
@@ -5292,7 +5281,7 @@
         <v>296.5</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>296.51</v>
       </c>
@@ -5300,7 +5289,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>297.01</v>
       </c>
@@ -5308,7 +5297,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>297.51</v>
       </c>
@@ -5316,7 +5305,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>298.01</v>
       </c>
@@ -5324,7 +5313,7 @@
         <v>298.5</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>298.51</v>
       </c>
@@ -5332,7 +5321,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>299.01</v>
       </c>
@@ -5340,7 +5329,7 @@
         <v>299.5</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>299.51</v>
       </c>

--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02CDA0-54E1-444C-B9F7-BCA9152A9A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,9 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Range Down</t>
+  </si>
+  <si>
+    <t>Zone 1</t>
   </si>
   <si>
     <t>Zone 2</t>
@@ -48,6 +50,9 @@
     <t>Zone 7</t>
   </si>
   <si>
+    <t>Zone 8</t>
+  </si>
+  <si>
     <t>Zone 9</t>
   </si>
   <si>
@@ -59,23 +64,11 @@
   <si>
     <t>Range Up</t>
   </si>
-  <si>
-    <t>Zone 1B</t>
-  </si>
-  <si>
-    <t>Zone 1A</t>
-  </si>
-  <si>
-    <t>Zone 8B</t>
-  </si>
-  <si>
-    <t>Zone 8A</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -493,62 +486,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O601"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M601"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -556,7 +543,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -564,7 +551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -572,7 +559,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -580,7 +567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -588,7 +575,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -596,7 +583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -604,7 +591,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -612,7 +599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -620,7 +607,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -628,7 +615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -636,7 +623,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -644,7 +631,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -652,7 +639,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -660,7 +647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>

--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6475B88E-9105-4D5C-8FCB-2DB53723731D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F2FDF-FFDB-4BEA-AE5E-E12E9FD3D018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Range Down</t>
   </si>
@@ -60,10 +60,19 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 1</t>
+    <t>Zone 1A</t>
   </si>
   <si>
-    <t>Zone 8</t>
+    <t>Zone 1B</t>
+  </si>
+  <si>
+    <t>Zone 8A</t>
+  </si>
+  <si>
+    <t>Zone 8B</t>
+  </si>
+  <si>
+    <t>Zone 8C</t>
   </si>
 </sst>
 </file>
@@ -488,15 +497,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M601"/>
+  <dimension ref="A1:P601"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" customWidth="1"/>
+    <col min="5" max="11" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="7.54296875" customWidth="1"/>
+    <col min="14" max="14" width="7.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -507,37 +520,46 @@
         <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="K1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -545,7 +567,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -553,7 +575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -561,7 +583,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -569,7 +591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -577,7 +599,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -585,7 +607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -593,7 +615,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -601,7 +623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -609,7 +631,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -617,7 +639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -625,7 +647,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -633,7 +655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -641,7 +663,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -649,7 +671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>

--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F2FDF-FFDB-4BEA-AE5E-E12E9FD3D018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E17CEEC-4162-4BAD-9953-7EABAE8E0B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,19 +60,19 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 1A</t>
+    <t>Zone 1a</t>
   </si>
   <si>
-    <t>Zone 1B</t>
+    <t>Zone 1b</t>
   </si>
   <si>
-    <t>Zone 8A</t>
+    <t>Zone 8a</t>
   </si>
   <si>
-    <t>Zone 8B</t>
+    <t>Zone 8b</t>
   </si>
   <si>
-    <t>Zone 8C</t>
+    <t>Zone 8c</t>
   </si>
 </sst>
 </file>

--- a/public/file/Retail International Standard Rates Upload Template.xlsx
+++ b/public/file/Retail International Standard Rates Upload Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E17CEEC-4162-4BAD-9953-7EABAE8E0B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64D4DC4-1C6C-48D7-AA20-6DFF8B0D353B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Range Down</t>
   </si>
@@ -63,16 +63,13 @@
     <t>Zone 1a</t>
   </si>
   <si>
-    <t>Zone 1b</t>
-  </si>
-  <si>
     <t>Zone 8a</t>
   </si>
   <si>
-    <t>Zone 8b</t>
+    <t>Zone 12</t>
   </si>
   <si>
-    <t>Zone 8c</t>
+    <t>Zone 13</t>
   </si>
 </sst>
 </file>
@@ -497,19 +494,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P601"/>
+  <dimension ref="A1:O601"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.54296875" customWidth="1"/>
-    <col min="5" max="11" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="7.54296875" customWidth="1"/>
-    <col min="14" max="14" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -520,46 +518,43 @@
         <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -567,7 +562,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -575,7 +570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -583,7 +578,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -591,7 +586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -599,7 +594,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -607,7 +602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -615,7 +610,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -623,7 +618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -631,7 +626,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -639,7 +634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -647,7 +642,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -655,7 +650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -663,7 +658,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -671,7 +666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>
